--- a/static/data/exports/Retro_TR_AE_2023.xlsx
+++ b/static/data/exports/Retro_TR_AE_2023.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_AE_2023.xlsx
+++ b/static/data/exports/Retro_TR_AE_2023.xlsx
@@ -602,11 +602,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E3" t="n">
         <v>5811</v>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E12" t="n">
         <v>20119</v>
@@ -1594,11 +1594,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E19" t="n">
         <v>21486</v>
@@ -1842,11 +1842,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E23" t="n">
         <v>18343</v>
@@ -3702,11 +3702,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E53" t="n">
         <v>16177</v>
@@ -4012,11 +4012,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E58" t="n">
         <v>7077</v>
@@ -4384,11 +4384,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E64" t="n">
         <v>1796</v>
@@ -4570,11 +4570,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E67" t="n">
         <v>26422</v>
@@ -5252,11 +5252,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E78" t="n">
         <v>17308</v>
@@ -5562,11 +5562,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E83" t="n">
         <v>20988</v>
@@ -5934,11 +5934,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E89" t="n">
         <v>7606</v>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E101" t="n">
         <v>19404</v>
@@ -7112,11 +7112,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E108" t="n">
         <v>18452</v>
@@ -7422,11 +7422,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E113" t="n">
         <v>20039</v>
@@ -7794,11 +7794,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E119" t="n">
         <v>15648</v>
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E126" t="n">
         <v>6941</v>
@@ -8538,11 +8538,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E131" t="n">
         <v>19696</v>
@@ -8910,11 +8910,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E137" t="n">
         <v>4420</v>
@@ -9282,11 +9282,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E143" t="n">
         <v>10981</v>
@@ -9964,11 +9964,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E154" t="n">
         <v>8679</v>
@@ -10274,11 +10274,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E159" t="n">
         <v>12613</v>
@@ -11142,11 +11142,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E173" t="n">
         <v>18574</v>
@@ -11452,11 +11452,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E178" t="n">
         <v>19514</v>
@@ -11638,11 +11638,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E181" t="n">
         <v>20016</v>
@@ -12258,11 +12258,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E191" t="n">
         <v>19986</v>
@@ -12568,11 +12568,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E196" t="n">
         <v>17246</v>
@@ -12878,11 +12878,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E201" t="n">
         <v>14922</v>
@@ -13064,11 +13064,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E204" t="n">
         <v>21801</v>
@@ -13374,11 +13374,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E209" t="n">
         <v>4151</v>
@@ -13684,11 +13684,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E214" t="n">
         <v>13395</v>
@@ -14180,11 +14180,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E222" t="n">
         <v>6934</v>
@@ -14490,11 +14490,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E227" t="n">
         <v>11339</v>
@@ -15048,11 +15048,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E236" t="n">
         <v>12475</v>
@@ -15544,11 +15544,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E244" t="n">
         <v>13373</v>
@@ -16350,11 +16350,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E257" t="n">
         <v>7402</v>
@@ -17032,11 +17032,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E268" t="n">
         <v>14458</v>
@@ -17404,11 +17404,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E274" t="n">
         <v>16818</v>
@@ -17962,11 +17962,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E283" t="n">
         <v>20012</v>
@@ -18334,11 +18334,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E289" t="n">
         <v>17444</v>
@@ -19016,11 +19016,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E300" t="n">
         <v>19386</v>
@@ -19264,11 +19264,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E304" t="n">
         <v>13247</v>
@@ -19574,11 +19574,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E309" t="n">
         <v>9808</v>
@@ -19946,11 +19946,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E315" t="n">
         <v>10522</v>
